--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F54CB8-47E1-4357-8AC8-C7B1B2808854}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5A0BFD-943C-4507-9567-971079515858}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7476" windowHeight="8916" activeTab="2" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7476" windowHeight="8916" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
   <sheets>
     <sheet name="4. évf" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="139">
   <si>
     <t>Lecke</t>
   </si>
@@ -290,6 +290,162 @@
   </si>
   <si>
     <t>do jigsaw puzzles</t>
+  </si>
+  <si>
+    <t>bike</t>
+  </si>
+  <si>
+    <t>bicikli</t>
+  </si>
+  <si>
+    <t>camera</t>
+  </si>
+  <si>
+    <t>fényképezőgép</t>
+  </si>
+  <si>
+    <t>game console</t>
+  </si>
+  <si>
+    <t>játékkonzol</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>KARÓRA</t>
+  </si>
+  <si>
+    <t>MP4 player</t>
+  </si>
+  <si>
+    <t>MP4 lejátszó</t>
+  </si>
+  <si>
+    <t>skateboard</t>
+  </si>
+  <si>
+    <t>gördeszka</t>
+  </si>
+  <si>
+    <t>sunglasses</t>
+  </si>
+  <si>
+    <t>napszemüveg</t>
+  </si>
+  <si>
+    <t>rollerblades</t>
+  </si>
+  <si>
+    <t>körgorcsolya</t>
+  </si>
+  <si>
+    <t>headphones</t>
+  </si>
+  <si>
+    <t>fejhallgató</t>
+  </si>
+  <si>
+    <t>comics</t>
+  </si>
+  <si>
+    <t>képregény</t>
+  </si>
+  <si>
+    <t>laptop</t>
+  </si>
+  <si>
+    <t>CDs</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>DVDs</t>
+  </si>
+  <si>
+    <t>DVD</t>
+  </si>
+  <si>
+    <t>guys</t>
+  </si>
+  <si>
+    <t>srácok</t>
+  </si>
+  <si>
+    <t>idea</t>
+  </si>
+  <si>
+    <t>ötlet</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>ház</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>lots of</t>
+  </si>
+  <si>
+    <t>sok, rengeteg</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>later</t>
+  </si>
+  <si>
+    <t>később</t>
+  </si>
+  <si>
+    <t>sleepy</t>
+  </si>
+  <si>
+    <t>álmos</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>fáradt</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>óra</t>
+  </si>
+  <si>
+    <t>sleepover</t>
+  </si>
+  <si>
+    <t>ottalvós vendégség</t>
+  </si>
+  <si>
+    <t>favourites</t>
+  </si>
+  <si>
+    <t>kedvencek</t>
+  </si>
+  <si>
+    <t>possession</t>
+  </si>
+  <si>
+    <t>tulajdon</t>
+  </si>
+  <si>
+    <t>Watch out!</t>
+  </si>
+  <si>
+    <t>Vigyázz!</t>
   </si>
 </sst>
 </file>
@@ -756,7 +912,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -768,6 +924,303 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5A0BFD-943C-4507-9567-971079515858}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73A759C-4432-4636-BBB9-325EC448999B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7476" windowHeight="8916" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="223">
   <si>
     <t>Lecke</t>
   </si>
@@ -446,6 +446,258 @@
   </si>
   <si>
     <t>Vigyázz!</t>
+  </si>
+  <si>
+    <t>3b</t>
+  </si>
+  <si>
+    <t>It's cloudy.</t>
+  </si>
+  <si>
+    <t>Felhős az ég</t>
+  </si>
+  <si>
+    <t>It's cold.</t>
+  </si>
+  <si>
+    <t>Hideg van.</t>
+  </si>
+  <si>
+    <t>It's hot.</t>
+  </si>
+  <si>
+    <t>Meleg van.</t>
+  </si>
+  <si>
+    <t>It's raining.</t>
+  </si>
+  <si>
+    <t>Esik az eső.</t>
+  </si>
+  <si>
+    <t>It's snowing.</t>
+  </si>
+  <si>
+    <t>Esik a hó..</t>
+  </si>
+  <si>
+    <t>It's sunny.</t>
+  </si>
+  <si>
+    <t>Süt a nap.</t>
+  </si>
+  <si>
+    <t>It's windy.</t>
+  </si>
+  <si>
+    <t>Szeles az idő.</t>
+  </si>
+  <si>
+    <t>autumm</t>
+  </si>
+  <si>
+    <t>ősz</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>tavasz</t>
+  </si>
+  <si>
+    <t>summer</t>
+  </si>
+  <si>
+    <t>nyár</t>
+  </si>
+  <si>
+    <t>winter</t>
+  </si>
+  <si>
+    <t>tél</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>cselekvés</t>
+  </si>
+  <si>
+    <t>each other</t>
+  </si>
+  <si>
+    <t>egymást</t>
+  </si>
+  <si>
+    <t>laugh</t>
+  </si>
+  <si>
+    <t>nevet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">look for </t>
+  </si>
+  <si>
+    <t>keres</t>
+  </si>
+  <si>
+    <t>make a snowman</t>
+  </si>
+  <si>
+    <t>hóembert készít</t>
+  </si>
+  <si>
+    <t>online</t>
+  </si>
+  <si>
+    <t>play in the snow</t>
+  </si>
+  <si>
+    <t>játszik a hóban</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+  <si>
+    <t>eső</t>
+  </si>
+  <si>
+    <t>tell</t>
+  </si>
+  <si>
+    <t>mond</t>
+  </si>
+  <si>
+    <t>throw a snowball</t>
+  </si>
+  <si>
+    <t>hógolyózik</t>
+  </si>
+  <si>
+    <t>try</t>
+  </si>
+  <si>
+    <t>kipróbál</t>
+  </si>
+  <si>
+    <t>anyone</t>
+  </si>
+  <si>
+    <t>bárki</t>
+  </si>
+  <si>
+    <t>anywhere</t>
+  </si>
+  <si>
+    <t>bárhol</t>
+  </si>
+  <si>
+    <t>plan</t>
+  </si>
+  <si>
+    <t>terv</t>
+  </si>
+  <si>
+    <t>chat room</t>
+  </si>
+  <si>
+    <t>csetszoba</t>
+  </si>
+  <si>
+    <t>world</t>
+  </si>
+  <si>
+    <t>világ</t>
+  </si>
+  <si>
+    <t>Anyway,…</t>
+  </si>
+  <si>
+    <t>Egyébként,…</t>
+  </si>
+  <si>
+    <t>Guess what!</t>
+  </si>
+  <si>
+    <t>Képzeld!</t>
+  </si>
+  <si>
+    <t>What's the weather like?</t>
+  </si>
+  <si>
+    <t>Milyen az idő?</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t>can't stand</t>
+  </si>
+  <si>
+    <t>ki nem állhat</t>
+  </si>
+  <si>
+    <t>classical music</t>
+  </si>
+  <si>
+    <t>komolyzene</t>
+  </si>
+  <si>
+    <t>concert</t>
+  </si>
+  <si>
+    <t>koncert</t>
+  </si>
+  <si>
+    <t>orchestra</t>
+  </si>
+  <si>
+    <t>zenekar</t>
+  </si>
+  <si>
+    <t>practise</t>
+  </si>
+  <si>
+    <t>gyakorol,próbál</t>
+  </si>
+  <si>
+    <t>prefer</t>
+  </si>
+  <si>
+    <t>jobban szeret</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>as soon as possible</t>
+  </si>
+  <si>
+    <t>amilyen hamar csak lehet</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>jegyzet</t>
+  </si>
+  <si>
+    <t>I know.</t>
+  </si>
+  <si>
+    <t>Tudom.</t>
+  </si>
+  <si>
+    <t>I have no idea.</t>
+  </si>
+  <si>
+    <t>Fogalmam sincs.</t>
+  </si>
+  <si>
+    <t>What do you think…?</t>
+  </si>
+  <si>
+    <t>Mit gondolsz…?</t>
   </si>
 </sst>
 </file>
@@ -482,7 +734,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -912,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1221,6 +1474,457 @@
       </c>
       <c r="C28" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
